--- a/Pole/cases/结论.xlsx
+++ b/Pole/cases/结论.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowWidth="22515" windowHeight="7500"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="任意垫版本" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -509,10 +509,32 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -535,28 +557,6 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -831,7 +831,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -840,22 +843,19 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="24" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="24" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="24" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="24" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="24" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1184,7 +1184,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25"/>
-    <row r="2" ht="54" spans="2:11">
+    <row r="2" ht="40.5" spans="2:11">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1212,388 +1212,388 @@
       <c r="J2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="2:11">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="7">
         <v>63</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="7">
         <v>124</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="7">
         <v>582</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="7">
         <v>643</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="7">
         <v>1380</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="7">
         <v>1371</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="7">
         <v>1370</v>
       </c>
-      <c r="K3" s="12">
+      <c r="K3" s="8">
         <v>1285</v>
       </c>
     </row>
     <row r="4" spans="2:11">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="7">
         <v>106</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="7">
         <v>211</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="7">
         <v>625</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="7">
         <v>730</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="7">
         <v>1467</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="7">
         <v>1457</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="7">
         <v>1456</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="8">
         <v>1372</v>
       </c>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="7">
         <v>40</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="7">
         <v>80</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="7">
         <v>574</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="7">
         <v>614</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="7">
         <v>1366</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="7">
         <v>1356</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="7">
         <v>1355</v>
       </c>
-      <c r="K5" s="12">
+      <c r="K5" s="8">
         <v>1271</v>
       </c>
     </row>
     <row r="6" spans="2:11">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="7">
         <v>84</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="7">
         <v>168</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="7">
         <v>619</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="7">
         <v>702</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="7">
         <v>1454</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="7">
         <v>1445</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="7">
         <v>1444</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="8">
         <v>1359</v>
       </c>
     </row>
     <row r="7" spans="2:11">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="7">
         <v>61</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <v>121</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="7">
         <v>611</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="7">
         <v>671</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="7">
         <v>1438</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="7">
         <v>1428</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="7">
         <v>1427</v>
       </c>
-      <c r="K7" s="12">
+      <c r="K7" s="8">
         <v>1343</v>
       </c>
     </row>
     <row r="8" spans="2:11">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="7">
         <v>105</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="7">
         <v>208</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="7">
         <v>654</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="7">
         <v>758</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="7">
         <v>1525</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="7">
         <v>1515</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="7">
         <v>1514</v>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="8">
         <v>1430</v>
       </c>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="7">
         <v>63</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="7">
         <v>124</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="7">
         <v>825</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="7">
         <v>887</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="7">
         <v>1868</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="7">
         <v>1858</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="7">
         <v>1857</v>
       </c>
-      <c r="K9" s="12">
+      <c r="K9" s="8">
         <v>1773</v>
       </c>
     </row>
     <row r="10" spans="2:11">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="7">
         <v>106</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="7">
         <v>211</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="7">
         <v>869</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="7">
         <v>974</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="7">
         <v>1954</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="7">
         <v>1944</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="7">
         <v>1943</v>
       </c>
-      <c r="K10" s="12">
+      <c r="K10" s="8">
         <v>1859</v>
       </c>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="7">
         <v>62</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="7">
         <v>123</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="7">
         <v>733</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="7">
         <v>794</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="7">
         <v>1684</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="7">
         <v>1674</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="7">
         <v>1673</v>
       </c>
-      <c r="K11" s="12">
+      <c r="K11" s="8">
         <v>1589</v>
       </c>
     </row>
     <row r="12" spans="2:11">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="7">
         <v>105</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="7">
         <v>210</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="7">
         <v>777</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="7">
         <v>881</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="7">
         <v>1770</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="7">
         <v>1761</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="7">
         <v>1760</v>
       </c>
-      <c r="K12" s="12">
+      <c r="K12" s="8">
         <v>1675</v>
       </c>
     </row>
     <row r="13" spans="2:11">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="7">
         <v>61</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="7">
         <v>121</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="7">
         <v>854</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="7">
         <v>914</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="7">
         <v>1925</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="7">
         <v>1916</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="7">
         <v>1915</v>
       </c>
-      <c r="K13" s="12">
+      <c r="K13" s="8">
         <v>1830</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="2:11">
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="11">
         <v>105</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="11">
         <v>208</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="11">
         <v>898</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="11">
         <v>1001</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="12">
         <v>2012</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="11">
         <v>2002</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="11">
         <v>2001</v>
       </c>
       <c r="K14" s="13">
